--- a/epsilon-phi-core/src/Scripts/Case Studies/Private Assets/Commitment Pacing.xlsx
+++ b/epsilon-phi-core/src/Scripts/Case Studies/Private Assets/Commitment Pacing.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/repo/epsilon-psi/epsilon-phi-core/src/Scripts/Case Studies/Private Assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/Repositories/Python/epsilon-phi/epsilon-phi-core/src/Scripts/Case Studies/Private Assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21743637-BD44-5541-9454-79FA0C0F5808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B5AA5B-709F-DC45-969B-FD0068C9F835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="15580" windowHeight="19040" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23620" yWindow="4220" windowWidth="15580" windowHeight="19040" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolios" sheetId="2" r:id="rId1"/>
@@ -1017,35 +1017,35 @@
     <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6276,43 +6276,43 @@
   <sheetData>
     <row r="1" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="49"/>
-      <c r="B1" s="107" t="s">
+      <c r="B1" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107" t="s">
+      <c r="C1" s="113"/>
+      <c r="D1" s="113" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107" t="s">
+      <c r="E1" s="113"/>
+      <c r="F1" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107" t="s">
+      <c r="G1" s="113"/>
+      <c r="H1" s="113" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="113"/>
+      <c r="I1" s="114"/>
     </row>
     <row r="2" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="106">
+      <c r="B2" s="115">
         <v>0.745</v>
       </c>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106" t="s">
+      <c r="C2" s="115"/>
+      <c r="D2" s="115" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106">
+      <c r="E2" s="115"/>
+      <c r="F2" s="115">
         <v>0.36</v>
       </c>
-      <c r="G2" s="106"/>
-      <c r="H2" s="106">
+      <c r="G2" s="115"/>
+      <c r="H2" s="115">
         <v>0.15</v>
       </c>
-      <c r="I2" s="106"/>
+      <c r="I2" s="115"/>
     </row>
     <row r="3" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="51" t="s">
@@ -6402,64 +6402,64 @@
       <c r="A7" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="112">
+      <c r="B7" s="109">
         <v>0.04</v>
       </c>
-      <c r="C7" s="112"/>
-      <c r="D7" s="112">
+      <c r="C7" s="109"/>
+      <c r="D7" s="109">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E7" s="112"/>
-      <c r="F7" s="112">
+      <c r="E7" s="109"/>
+      <c r="F7" s="109">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="G7" s="112"/>
-      <c r="H7" s="112">
+      <c r="G7" s="109"/>
+      <c r="H7" s="109">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="I7" s="112"/>
+      <c r="I7" s="109"/>
     </row>
     <row r="8" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="111">
+      <c r="B8" s="110">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111">
+      <c r="C8" s="110"/>
+      <c r="D8" s="110">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="E8" s="111"/>
-      <c r="F8" s="111">
+      <c r="E8" s="110"/>
+      <c r="F8" s="110">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="G8" s="111"/>
-      <c r="H8" s="111">
+      <c r="G8" s="110"/>
+      <c r="H8" s="110">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="I8" s="111"/>
+      <c r="I8" s="110"/>
     </row>
     <row r="9" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="110">
+      <c r="B9" s="111">
         <v>0.6</v>
       </c>
-      <c r="C9" s="110"/>
-      <c r="D9" s="110">
+      <c r="C9" s="111"/>
+      <c r="D9" s="111">
         <v>0.59</v>
       </c>
-      <c r="E9" s="110"/>
-      <c r="F9" s="110">
+      <c r="E9" s="111"/>
+      <c r="F9" s="111">
         <v>0.53</v>
       </c>
-      <c r="G9" s="110"/>
-      <c r="H9" s="110">
+      <c r="G9" s="111"/>
+      <c r="H9" s="111">
         <v>0.49</v>
       </c>
-      <c r="I9" s="110"/>
+      <c r="I9" s="111"/>
     </row>
     <row r="10" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="54" t="s">
@@ -6486,22 +6486,22 @@
       <c r="A11" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="109" t="s">
+      <c r="B11" s="112" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="109"/>
-      <c r="D11" s="109" t="s">
+      <c r="C11" s="112"/>
+      <c r="D11" s="112" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="109"/>
-      <c r="F11" s="109" t="s">
+      <c r="E11" s="112"/>
+      <c r="F11" s="112" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="109"/>
-      <c r="H11" s="109" t="s">
+      <c r="G11" s="112"/>
+      <c r="H11" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="109"/>
+      <c r="I11" s="112"/>
     </row>
     <row r="12" spans="1:9" s="8" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="55" t="s">
@@ -6794,64 +6794,64 @@
       <c r="A23" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="114">
+      <c r="B23" s="106">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="C23" s="114"/>
-      <c r="D23" s="114">
+      <c r="C23" s="106"/>
+      <c r="D23" s="106">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="E23" s="114"/>
-      <c r="F23" s="114">
+      <c r="E23" s="106"/>
+      <c r="F23" s="106">
         <v>6.3E-2</v>
       </c>
-      <c r="G23" s="114"/>
-      <c r="H23" s="114">
+      <c r="G23" s="106"/>
+      <c r="H23" s="106">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="I23" s="114"/>
+      <c r="I23" s="106"/>
     </row>
     <row r="24" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="114">
+      <c r="B24" s="106">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C24" s="114"/>
-      <c r="D24" s="114">
+      <c r="C24" s="106"/>
+      <c r="D24" s="106">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="E24" s="114"/>
-      <c r="F24" s="114">
+      <c r="E24" s="106"/>
+      <c r="F24" s="106">
         <v>0.16200000000000001</v>
       </c>
-      <c r="G24" s="114"/>
-      <c r="H24" s="114">
+      <c r="G24" s="106"/>
+      <c r="H24" s="106">
         <v>0.24299999999999999</v>
       </c>
-      <c r="I24" s="114"/>
+      <c r="I24" s="106"/>
     </row>
     <row r="25" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="115">
+      <c r="B25" s="107">
         <v>0</v>
       </c>
-      <c r="C25" s="115"/>
-      <c r="D25" s="115">
+      <c r="C25" s="107"/>
+      <c r="D25" s="107">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="E25" s="115"/>
-      <c r="F25" s="115">
+      <c r="E25" s="107"/>
+      <c r="F25" s="107">
         <v>0.14899999999999999</v>
       </c>
-      <c r="G25" s="115"/>
-      <c r="H25" s="115">
+      <c r="G25" s="107"/>
+      <c r="H25" s="107">
         <v>0.253</v>
       </c>
-      <c r="I25" s="115"/>
+      <c r="I25" s="107"/>
     </row>
     <row r="26" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="63" t="s">
@@ -6870,64 +6870,64 @@
       <c r="A27" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="114">
+      <c r="B27" s="106">
         <v>0.23799999999999999</v>
       </c>
-      <c r="C27" s="114"/>
-      <c r="D27" s="114">
+      <c r="C27" s="106"/>
+      <c r="D27" s="106">
         <v>0.27900000000000003</v>
       </c>
-      <c r="E27" s="114"/>
-      <c r="F27" s="114">
+      <c r="E27" s="106"/>
+      <c r="F27" s="106">
         <v>0.314</v>
       </c>
-      <c r="G27" s="114"/>
-      <c r="H27" s="114">
+      <c r="G27" s="106"/>
+      <c r="H27" s="106">
         <v>0.33700000000000002</v>
       </c>
-      <c r="I27" s="114"/>
+      <c r="I27" s="106"/>
     </row>
     <row r="28" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="114">
+      <c r="B28" s="106">
         <v>0.04</v>
       </c>
-      <c r="C28" s="114"/>
-      <c r="D28" s="114">
+      <c r="C28" s="106"/>
+      <c r="D28" s="106">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="E28" s="114"/>
-      <c r="F28" s="114">
+      <c r="E28" s="106"/>
+      <c r="F28" s="106">
         <v>0.14299999999999999</v>
       </c>
-      <c r="G28" s="114"/>
-      <c r="H28" s="114">
+      <c r="G28" s="106"/>
+      <c r="H28" s="106">
         <v>0.187</v>
       </c>
-      <c r="I28" s="114"/>
+      <c r="I28" s="106"/>
     </row>
     <row r="29" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="114">
+      <c r="B29" s="106">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C29" s="114"/>
-      <c r="D29" s="114">
+      <c r="C29" s="106"/>
+      <c r="D29" s="106">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="E29" s="114"/>
-      <c r="F29" s="114">
+      <c r="E29" s="106"/>
+      <c r="F29" s="106">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="G29" s="114"/>
-      <c r="H29" s="114">
+      <c r="G29" s="106"/>
+      <c r="H29" s="106">
         <v>0.108</v>
       </c>
-      <c r="I29" s="114"/>
+      <c r="I29" s="106"/>
     </row>
     <row r="30" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="55" t="s">
@@ -7321,56 +7321,11 @@
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="B5:C5"/>
@@ -7384,11 +7339,56 @@
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H28:I28"/>
   </mergeCells>
   <conditionalFormatting sqref="B14:I21">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
@@ -9615,7 +9615,7 @@
         <v>0.5</v>
       </c>
       <c r="E2" s="52">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F2" s="31">
         <v>0</v>
@@ -9635,7 +9635,7 @@
         <v>0.5</v>
       </c>
       <c r="E3" s="52">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F3" s="52">
         <v>0</v>
